--- a/Pruebas calificadas/COLEGIO PAULO FREIRE (IED)-1005_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO PAULO FREIRE (IED)-1005_CALIFICADO.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ62"/>
+  <dimension ref="A1:AZ63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -16211,6 +16211,179 @@
         <v/>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>CONTROL</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>111001107760</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>COLEGIO PAULO FREIRE (IED)</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>MARIANA ESPINOSA RAMIREZ</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>1022984739</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>1105</v>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>LENGUAJE</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr"/>
+      <c r="P63" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="U63" s="2" t="inlineStr"/>
+      <c r="V63" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr"/>
+      <c r="X63" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr"/>
+      <c r="Z63" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr"/>
+      <c r="AB63" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr"/>
+      <c r="AD63" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AE63" s="2" t="inlineStr"/>
+      <c r="AF63" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AG63" s="2" t="inlineStr"/>
+      <c r="AH63" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AI63" s="2" t="inlineStr"/>
+      <c r="AJ63" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AK63" s="2" t="inlineStr"/>
+      <c r="AL63" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AM63" s="2" t="inlineStr"/>
+      <c r="AN63" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AO63" s="2" t="inlineStr"/>
+      <c r="AP63" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AQ63" s="2" t="inlineStr"/>
+      <c r="AR63" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AS63" s="2" t="inlineStr"/>
+      <c r="AT63" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AU63" s="2" t="inlineStr"/>
+      <c r="AV63" s="3" t="inlineStr">
+        <is>
+          <t>INCORRECTO</t>
+        </is>
+      </c>
+      <c r="AW63" s="5">
+        <f>COUNTIF(J63:AV63,"CORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AX63" s="5">
+        <f>COUNTIF(J63:AV63,"INCORRECTO")</f>
+        <v/>
+      </c>
+      <c r="AY63" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ63" s="6">
+        <f>AW63/AY63</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Pruebas calificadas/COLEGIO PAULO FREIRE (IED)-1005_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO PAULO FREIRE (IED)-1005_CALIFICADO.xlsx
@@ -807,11 +807,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001107760</t>
@@ -1060,11 +1056,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001107760</t>
@@ -1313,11 +1305,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001107760</t>
@@ -1566,11 +1554,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001107760</t>
@@ -1819,11 +1803,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001107760</t>
@@ -2072,11 +2052,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001107760</t>
@@ -2325,11 +2301,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001107760</t>
@@ -2574,11 +2546,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001107760</t>
@@ -2827,11 +2795,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001107760</t>
@@ -3080,11 +3044,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001107760</t>
@@ -3333,11 +3293,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001107760</t>
@@ -3586,11 +3542,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001107760</t>
@@ -3839,11 +3791,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001107760</t>
@@ -4092,11 +4040,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001107760</t>
@@ -4345,11 +4289,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001107760</t>
@@ -4598,11 +4538,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001107760</t>
@@ -4851,11 +4787,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001107760</t>
@@ -5104,11 +5036,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001107760</t>
@@ -5357,11 +5285,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001107760</t>
@@ -5610,11 +5534,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001107760</t>
@@ -5863,11 +5783,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001107760</t>
@@ -6116,11 +6032,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001107760</t>
@@ -6369,11 +6281,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001107760</t>
@@ -6622,11 +6530,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001107760</t>
@@ -6875,11 +6779,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001107760</t>
@@ -7120,11 +7020,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001107760</t>
@@ -7373,11 +7269,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001107760</t>
@@ -7626,11 +7518,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001107760</t>
@@ -7879,11 +7767,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001107760</t>
@@ -8132,11 +8016,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001107760</t>
@@ -8385,11 +8265,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001107760</t>
@@ -8638,11 +8514,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001107760</t>
@@ -8891,11 +8763,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111001107760</t>
@@ -9144,11 +9012,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111001107760</t>
@@ -9397,11 +9261,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>111001107760</t>
@@ -9650,11 +9510,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>111001107760</t>
@@ -9903,11 +9759,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>111001107760</t>
@@ -10156,11 +10008,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>111001107760</t>
@@ -10409,11 +10257,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>111001107760</t>
@@ -10662,11 +10506,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>111001107760</t>
@@ -10915,11 +10755,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t>111001107760</t>
@@ -11168,11 +11004,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
           <t>111001107760</t>
@@ -11421,11 +11253,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
           <t>111001107760</t>
@@ -11674,11 +11502,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
           <t>111001107760</t>
@@ -11927,11 +11751,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
           <t>111001107760</t>
@@ -12180,11 +12000,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="2" t="inlineStr">
         <is>
           <t>111001107760</t>
@@ -12433,11 +12249,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
           <t>111001107760</t>
@@ -12682,11 +12494,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
           <t>111001107760</t>
@@ -12935,11 +12743,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
           <t>111001107760</t>
@@ -13188,11 +12992,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
           <t>111001107760</t>
@@ -13441,11 +13241,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A52" s="2" t="inlineStr"/>
       <c r="B52" s="2" t="inlineStr">
         <is>
           <t>111001107760</t>
@@ -13694,11 +13490,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
           <t>111001107760</t>
@@ -13947,11 +13739,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="inlineStr"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
           <t>111001107760</t>
@@ -14200,11 +13988,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="inlineStr"/>
       <c r="B55" s="2" t="inlineStr">
         <is>
           <t>111001107760</t>
@@ -14453,11 +14237,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="inlineStr"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
           <t>111001107760</t>
@@ -14706,11 +14486,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="inlineStr"/>
       <c r="B57" s="2" t="inlineStr">
         <is>
           <t>111001107760</t>
@@ -14951,11 +14727,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
           <t>111001107760</t>
@@ -15204,11 +14976,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="inlineStr"/>
       <c r="B59" s="2" t="inlineStr">
         <is>
           <t>111001107760</t>
@@ -15453,11 +15221,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="inlineStr"/>
       <c r="B60" s="2" t="inlineStr">
         <is>
           <t>111001107760</t>
@@ -15706,11 +15470,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A61" s="2" t="inlineStr"/>
       <c r="B61" s="2" t="inlineStr">
         <is>
           <t>111001107760</t>
@@ -15959,11 +15719,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A62" s="2" t="inlineStr"/>
       <c r="B62" s="2" t="inlineStr">
         <is>
           <t>111001107760</t>
@@ -16212,11 +15968,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A63" s="2" t="inlineStr"/>
       <c r="B63" s="2" t="inlineStr">
         <is>
           <t>111001107760</t>
